--- a/data/employees/EMP003/AST-EMP003-06.xlsx
+++ b/data/employees/EMP003/AST-EMP003-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Resource Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Resource Utilization - Taylor Miller (IT)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Taylor Miller | Role: Lead | Location: Bengaluru | Date: 2025-01-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CPU %</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Memory %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Disk %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Network (Mbps)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>87</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD-APP-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>70</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD-SQL-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88</v>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>64</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-WEB-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-API-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" t="n">
-        <v>62</v>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>450</v>
+        <v>66</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>96</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>93</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>83</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>91</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>82</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>84</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>72</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>86</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>69</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>73</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>97</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>81</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>67</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>66</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>99</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>73</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp003 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>98</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP003 contributes to ast emp003 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>